--- a/bioinformatics-analysis/resources/patient-meta-en.xlsx
+++ b/bioinformatics-analysis/resources/patient-meta-en.xlsx
@@ -1,138 +1,101 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\private\bioinfo-view\bio2023\code\bioinfo-view-be\bioinformatics-analysis\resources\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0890608-89BA-4ECC-8EAD-1D35598C7631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3 xr6 xr10 x15">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11208"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="27096" windowHeight="16296" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="15800" windowWidth="28040" xWindow="4240" yWindow="640"/>
   </bookViews>
   <sheets>
-    <sheet name="患者" sheetId="1" r:id="rId1"/>
+    <sheet name="患者" sheetId="2" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="144525" concurrentCalc="0"/>
+  <calcPr calcMode="auto"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Gender</t>
-  </si>
-  <si>
-    <t>Date of Birth</t>
-  </si>
-  <si>
-    <t>ID card</t>
-  </si>
-  <si>
-    <t>Home Address</t>
-  </si>
-  <si>
-    <t>Submission Unit</t>
-  </si>
-  <si>
-    <t>Treating Physician</t>
-  </si>
-  <si>
-    <t>Clinical Diagnosis</t>
-  </si>
-  <si>
-    <t>Tumor Staging</t>
-  </si>
-  <si>
-    <t>Genetic Disease</t>
-  </si>
-  <si>
-    <t>Family History</t>
-  </si>
-  <si>
-    <t>Grug Using History</t>
-  </si>
-  <si>
-    <t>Smoking</t>
-  </si>
-  <si>
-    <t>Alcohol Drinking</t>
-  </si>
-  <si>
-    <t>Viral Infection</t>
-  </si>
-  <si>
-    <t>Treatment History</t>
-  </si>
-  <si>
-    <t>Prognosis Information</t>
-  </si>
-  <si>
-    <t>Prognosis Time(day)</t>
-  </si>
-  <si>
-    <t>Time of Recurrence(day)</t>
-  </si>
-  <si>
-    <t>Survival Time(day)</t>
-  </si>
-  <si>
-    <t>Gestation(Week)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pregnancy Status</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t xml:space="preserve">  </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy/m/d"/>
+  </numFmts>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill patternType="none">
+        <fgColor/>
+        <bgColor/>
+      </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <fgColor/>
+        <bgColor/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -142,29 +105,27 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="4">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="true" applyProtection="false" borderId="1" fillId="0" fontId="1" numFmtId="164" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -177,7 +138,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -219,7 +180,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -252,9 +213,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -287,6 +265,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -429,117 +424,172 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V3"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3 xr6 xr10 x15">
+  <sheetPr>
+    <outlinePr summaryBelow="false" summaryRight="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="19"/>
   <cols>
-    <col min="4" max="4" width="12.44140625" customWidth="1"/>
-    <col min="10" max="10" width="15.5546875" customWidth="1"/>
-    <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="2" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="3" min="3" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="4" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="5" min="5" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="6" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="7" min="7" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="8" min="8" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="9" min="9" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="10" min="10" style="0" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="11" min="11" style="0" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="12" min="12" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="13" min="13" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="14" min="14" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="15" min="15" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="16" min="16" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="17" min="17" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="18" min="18" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="19" min="19" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="20" min="20" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="21" min="21" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="22" min="22" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="23" min="23" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="24" min="24" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="25" min="25" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="26" min="26" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="27" min="27" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="28" min="28" style="0" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>14</v>
-      </c>
-      <c r="R1" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" t="s">
-        <v>16</v>
-      </c>
-      <c r="T1" t="s">
-        <v>17</v>
-      </c>
-      <c r="U1" t="s">
-        <v>18</v>
-      </c>
-      <c r="V1" t="s">
-        <v>19</v>
+    <row customHeight="true" ht="17" r="1">
+      <c r="A1" s="3" t="str">
+        <v>Name</v>
+      </c>
+      <c r="B1" s="3" t="str">
+        <v>Gender</v>
+      </c>
+      <c r="C1" s="3" t="str">
+        <v>Date of Birth</v>
+      </c>
+      <c r="D1" s="3" t="str">
+        <v>ID card</v>
+      </c>
+      <c r="E1" s="2" t="str">
+        <v>Home Address</v>
+      </c>
+      <c r="F1" s="3" t="str">
+        <v>Submission Unit</v>
+      </c>
+      <c r="G1" s="3" t="str">
+        <v>Treating Physician</v>
+      </c>
+      <c r="H1" s="3" t="str">
+        <v>Clinical Diagnosis</v>
+      </c>
+      <c r="I1" s="2" t="str">
+        <v>Tumor Staging</v>
+      </c>
+      <c r="J1" s="2" t="str">
+        <v>Genetic Disease</v>
+      </c>
+      <c r="K1" s="2" t="str">
+        <v>Gestation(Week)</v>
+      </c>
+      <c r="L1" s="2" t="str">
+        <v>Pregnancy Status</v>
+      </c>
+      <c r="M1" s="2" t="str">
+        <v>Family History</v>
+      </c>
+      <c r="N1" s="2" t="str">
+        <v>Grug Using History</v>
+      </c>
+      <c r="O1" s="2" t="str">
+        <v>Smoking</v>
+      </c>
+      <c r="P1" s="2" t="str">
+        <v>Alcohol Drinking</v>
+      </c>
+      <c r="Q1" s="2" t="str">
+        <v>Viral Infection</v>
+      </c>
+      <c r="R1" s="2" t="str">
+        <v>Treatment History</v>
+      </c>
+      <c r="S1" s="2" t="str">
+        <v>Prognosis Information</v>
+      </c>
+      <c r="T1" s="2" t="str">
+        <v>Prognosis Time(day)</v>
+      </c>
+      <c r="U1" s="2" t="str">
+        <v>Time of Recurrence(day)</v>
+      </c>
+      <c r="V1" s="2" t="str">
+        <v>Survival Time(day)</v>
+      </c>
+      <c r="W1" s="2" t="str">
+        <v>General Pathology Number</v>
+      </c>
+      <c r="X1" s="2" t="str">
+        <v>Molecular Pathology Number</v>
+      </c>
+      <c r="Y1" s="2" t="str">
+        <v>Submitting Department</v>
+      </c>
+      <c r="Z1" s="2" t="str">
+        <v>Patient Phone Number</v>
+      </c>
+      <c r="AA1" s="2" t="str">
+        <v>Outpatient/Inpatient Number</v>
+      </c>
+      <c r="AB1" s="2" t="str">
+        <v>Bed Number</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C2" s="2"/>
+    <row customHeight="true" ht="17" r="2">
+      <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C3" s="2"/>
+    <row customHeight="true" ht="17" r="3">
+      <c r="C3" s="1"/>
     </row>
+    <row customHeight="true" ht="17" r="4"/>
+    <row customHeight="true" ht="17" r="5"/>
+    <row customHeight="true" ht="17" r="6"/>
+    <row customHeight="true" ht="17" r="7"/>
+    <row customHeight="true" ht="17" r="8"/>
+    <row customHeight="true" ht="17" r="9"/>
+    <row customHeight="true" ht="17" r="10"/>
+    <row customHeight="true" ht="17" r="11"/>
+    <row customHeight="true" ht="17" r="12"/>
+    <row customHeight="true" ht="17" r="13"/>
+    <row customHeight="true" ht="17" r="14"/>
+    <row customHeight="true" ht="17" r="15"/>
+    <row customHeight="true" ht="17" r="16"/>
+    <row customHeight="true" ht="17" r="17"/>
+    <row customHeight="true" ht="17" r="18"/>
+    <row customHeight="true" ht="17" r="19"/>
+    <row customHeight="true" ht="17" r="20"/>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P1:P1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="O1:O20 Q1:Q20" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="P1:P20" type="list">
       <formula1>"Yes,NO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O1:O1048576 Q1:Q1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation allowBlank="true" errorStyle="stop" showErrorMessage="true" sqref="B1:B20" type="list">
       <formula1>"Male,Female"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter>
-    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Arial"&amp;10&amp;K000000 Internal</oddFooter>
-  </headerFooter>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{06530cf4-8573-4c29-a912-bbcdac835909}" enabled="1" method="Standard" siteId="{ecaa386b-c8df-4ce0-ad01-740cbdb5ba55}" contentBits="2" removed="0"/>
-</clbl:labelList>
 </file>